--- a/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0002T0006Z000C1N28_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0002T0006Z000C1N28_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>25.81945242297353</v>
+        <v>4.195661018733198</v>
       </c>
       <c r="D2" t="n">
-        <v>25.64511927693582</v>
+        <v>4.167331882502071</v>
       </c>
       <c r="E2" t="n">
-        <v>11.90093111140814</v>
+        <v>1.933901305603823</v>
       </c>
       <c r="F2" t="n">
-        <v>12.64044446842775</v>
+        <v>2.054072226119509</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>24.57428420389409</v>
+        <v>3.99332118313279</v>
       </c>
       <c r="D3" t="n">
-        <v>24.45232099868077</v>
+        <v>3.973502162285625</v>
       </c>
       <c r="E3" t="n">
-        <v>11.90093111140814</v>
+        <v>1.933901305603823</v>
       </c>
       <c r="F3" t="n">
-        <v>12.64044446842775</v>
+        <v>2.054072226119509</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>37.22063652513286</v>
+        <v>6.04835343533409</v>
       </c>
       <c r="D4" t="n">
-        <v>36.14003565492434</v>
+        <v>5.872755793925205</v>
       </c>
       <c r="E4" t="n">
-        <v>11.90093111140814</v>
+        <v>1.933901305603823</v>
       </c>
       <c r="F4" t="n">
-        <v>12.64044446842775</v>
+        <v>2.054072226119509</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>41.72367978742776</v>
+        <v>6.780097965457011</v>
       </c>
       <c r="D5" t="n">
-        <v>40.09386295455933</v>
+        <v>6.515252730115892</v>
       </c>
       <c r="E5" t="n">
-        <v>11.90093111140814</v>
+        <v>1.933901305603823</v>
       </c>
       <c r="F5" t="n">
-        <v>12.64044446842775</v>
+        <v>2.054072226119509</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>30.7001628660175</v>
+        <v>4.988776465727844</v>
       </c>
       <c r="D6" t="n">
-        <v>34.70521968967894</v>
+        <v>5.639598199572828</v>
       </c>
       <c r="E6" t="n">
-        <v>11.90093111140814</v>
+        <v>1.933901305603823</v>
       </c>
       <c r="F6" t="n">
-        <v>12.64044446842775</v>
+        <v>2.054072226119509</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>17.75375541040655</v>
+        <v>2.884985254191065</v>
       </c>
       <c r="D7" t="n">
-        <v>16.29115567025123</v>
+        <v>2.647312796415825</v>
       </c>
       <c r="E7" t="n">
-        <v>11.90093111140814</v>
+        <v>1.933901305603823</v>
       </c>
       <c r="F7" t="n">
-        <v>12.64044446842775</v>
+        <v>2.054072226119509</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>15.96868217803386</v>
+        <v>2.594910853930503</v>
       </c>
       <c r="D8" t="n">
-        <v>29.00513302038472</v>
+        <v>4.713334115812517</v>
       </c>
       <c r="E8" t="n">
-        <v>11.90093111140814</v>
+        <v>1.933901305603823</v>
       </c>
       <c r="F8" t="n">
-        <v>12.64044446842775</v>
+        <v>2.054072226119509</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>35.01272460756221</v>
+        <v>5.689567748728859</v>
       </c>
       <c r="D9" t="n">
-        <v>36.62972416496486</v>
+        <v>5.95233017680679</v>
       </c>
       <c r="E9" t="n">
-        <v>11.90093111140814</v>
+        <v>1.933901305603823</v>
       </c>
       <c r="F9" t="n">
-        <v>12.64044446842775</v>
+        <v>2.054072226119509</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>12.75025501303622</v>
+        <v>2.071916439618386</v>
       </c>
       <c r="D10" t="n">
-        <v>12.10594917849367</v>
+        <v>1.967216741505222</v>
       </c>
       <c r="E10" t="n">
-        <v>11.90093111140814</v>
+        <v>1.933901305603823</v>
       </c>
       <c r="F10" t="n">
-        <v>12.64044446842775</v>
+        <v>2.054072226119509</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>17.06604816587601</v>
+        <v>2.773232826954852</v>
       </c>
       <c r="D11" t="n">
-        <v>39.09804868271348</v>
+        <v>6.353432910940941</v>
       </c>
       <c r="E11" t="n">
-        <v>11.90093111140814</v>
+        <v>1.933901305603823</v>
       </c>
       <c r="F11" t="n">
-        <v>12.64044446842775</v>
+        <v>2.054072226119509</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>39.99062390110962</v>
+        <v>6.498476383930313</v>
       </c>
       <c r="D12" t="n">
-        <v>43.60812587430411</v>
+        <v>7.086320454574418</v>
       </c>
       <c r="E12" t="n">
-        <v>11.90093111140814</v>
+        <v>1.933901305603823</v>
       </c>
       <c r="F12" t="n">
-        <v>12.64044446842775</v>
+        <v>2.054072226119509</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>35.22782990761707</v>
+        <v>5.724522359987774</v>
       </c>
       <c r="D13" t="n">
-        <v>42.94627887840575</v>
+        <v>6.978770317740935</v>
       </c>
       <c r="E13" t="n">
-        <v>11.90093111140814</v>
+        <v>1.933901305603823</v>
       </c>
       <c r="F13" t="n">
-        <v>12.64044446842775</v>
+        <v>2.054072226119509</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3299189583866465</v>
+        <v>0.05361183073783006</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2799865911824822</v>
+        <v>0.04549782106715336</v>
       </c>
       <c r="E14" t="n">
-        <v>11.90093111140814</v>
+        <v>1.933901305603823</v>
       </c>
       <c r="F14" t="n">
-        <v>12.64044446842775</v>
+        <v>2.054072226119509</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
